--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134232906</v>
+        <v>135136407</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Kviddtjärnen, Gränsjön, Kviddtjärnen, Gränsjön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499887</v>
+        <v>499941</v>
       </c>
       <c r="R2" t="n">
-        <v>6621451</v>
+        <v>6621317</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,64 +775,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232907</v>
+        <v>135134046</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499863</v>
+        <v>499686</v>
       </c>
       <c r="R3" t="n">
-        <v>6621478</v>
+        <v>6621303</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Äldre ringhack på gran. Färsk barkfläkning ovanför. Märkt med rött band.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,64 +895,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232908</v>
+        <v>135136673</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Kviddtjärnen, Gränsjön, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499922</v>
+        <v>499937</v>
       </c>
       <c r="R4" t="n">
-        <v>6621337</v>
+        <v>6621393</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,27 +977,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Äldre tretåhack på gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,64 +1012,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134232909</v>
+        <v>135137492</v>
       </c>
       <c r="B5" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499860</v>
+        <v>499799</v>
       </c>
       <c r="R5" t="n">
-        <v>6621240</v>
+        <v>6621444</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,27 +1094,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Färsk barkfläkning och påbörjade ringhack med savflöde av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134232855</v>
+        <v>135135968</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1172,19 +1174,35 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499858</v>
+        <v>499864</v>
       </c>
       <c r="R6" t="n">
-        <v>6621241</v>
+        <v>6621255</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,27 +1226,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fjädrar fr höna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134232856</v>
+        <v>135136960</v>
       </c>
       <c r="B7" t="n">
-        <v>98060</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,41 +1284,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Kviddtjärnen, Gränsjön, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499825</v>
+        <v>499933</v>
       </c>
       <c r="R7" t="n">
-        <v>6621232</v>
+        <v>6621422</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,27 +1343,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,15 +1373,2620 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135152620</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499888</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6621280</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135137648</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499790</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6621466</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Och kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134232906</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499887</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6621451</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134232907</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499863</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6621478</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134232908</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499922</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6621337</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134232909</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499860</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6621240</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135134139</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499712</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6621314</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135134238</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499725</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6621314</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135134506</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499755</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6621280</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135134677</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499824</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6621297</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135134706</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499838</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6621289</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135135788</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499855</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6621252</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135136001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499871</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6621255</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135136063</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499899</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6621248</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135136115</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499917</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6621282</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135136391</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499940</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6621317</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135136466</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499950</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6621333</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135136984</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499932</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6621423</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135137057</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499912</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6621430</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135137666</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499790</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6621466</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134232855</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499858</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6621241</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134232856</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>499825</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6621232</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135137648</v>
+        <v>135191221</v>
       </c>
       <c r="B9" t="n">
-        <v>8449</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,39 +1498,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Kviddtjärnen, Gränsjön, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499790</v>
+        <v>499962</v>
       </c>
       <c r="R9" t="n">
-        <v>6621466</v>
+        <v>6621359</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1557,27 +1557,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Och kläckhål.</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134232906</v>
+        <v>135137648</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>8449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,41 +1600,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499887</v>
+        <v>499790</v>
       </c>
       <c r="R10" t="n">
-        <v>6621451</v>
+        <v>6621466</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,27 +1659,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Och kläckhål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,19 +1694,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134232907</v>
+        <v>134232906</v>
       </c>
       <c r="B11" t="n">
         <v>99112</v>
@@ -1759,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499863</v>
+        <v>499887</v>
       </c>
       <c r="R11" t="n">
-        <v>6621478</v>
+        <v>6621451</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1794,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1836,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134232908</v>
+        <v>134232907</v>
       </c>
       <c r="B12" t="n">
         <v>99112</v>
@@ -1875,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499922</v>
+        <v>499863</v>
       </c>
       <c r="R12" t="n">
-        <v>6621337</v>
+        <v>6621478</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1910,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1952,7 +1938,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134232909</v>
+        <v>134232908</v>
       </c>
       <c r="B13" t="n">
         <v>99112</v>
@@ -1991,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499860</v>
+        <v>499922</v>
       </c>
       <c r="R13" t="n">
-        <v>6621240</v>
+        <v>6621337</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2068,7 +2054,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135134139</v>
+        <v>134232909</v>
       </c>
       <c r="B14" t="n">
         <v>99112</v>
@@ -2101,29 +2087,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499712</v>
+        <v>499860</v>
       </c>
       <c r="R14" t="n">
-        <v>6621314</v>
+        <v>6621240</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2147,22 +2123,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,19 +2158,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135134238</v>
+        <v>135134139</v>
       </c>
       <c r="B15" t="n">
         <v>99112</v>
@@ -2219,7 +2200,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2238,7 +2219,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499725</v>
+        <v>499712</v>
       </c>
       <c r="R15" t="n">
         <v>6621314</v>
@@ -2273,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135134506</v>
+        <v>135134238</v>
       </c>
       <c r="B16" t="n">
         <v>99112</v>
@@ -2340,7 +2321,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2359,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499755</v>
+        <v>499725</v>
       </c>
       <c r="R16" t="n">
-        <v>6621280</v>
+        <v>6621314</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2394,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2404,7 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,7 +2412,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135134677</v>
+        <v>135134506</v>
       </c>
       <c r="B17" t="n">
         <v>99112</v>
@@ -2461,7 +2442,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2480,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499824</v>
+        <v>499755</v>
       </c>
       <c r="R17" t="n">
-        <v>6621297</v>
+        <v>6621280</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2515,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135134706</v>
+        <v>135134677</v>
       </c>
       <c r="B18" t="n">
         <v>99112</v>
@@ -2580,7 +2561,11 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2597,10 +2582,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499838</v>
+        <v>499824</v>
       </c>
       <c r="R18" t="n">
-        <v>6621289</v>
+        <v>6621297</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2632,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2642,7 +2627,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,7 +2654,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135135788</v>
+        <v>135134706</v>
       </c>
       <c r="B19" t="n">
         <v>99112</v>
@@ -2697,11 +2682,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2718,10 +2699,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499855</v>
+        <v>499838</v>
       </c>
       <c r="R19" t="n">
-        <v>6621252</v>
+        <v>6621289</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2753,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,7 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,7 +2771,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135136001</v>
+        <v>135135788</v>
       </c>
       <c r="B20" t="n">
         <v>99112</v>
@@ -2820,7 +2801,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,10 +2820,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499871</v>
+        <v>499855</v>
       </c>
       <c r="R20" t="n">
-        <v>6621255</v>
+        <v>6621252</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2874,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2884,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,7 +2892,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135136063</v>
+        <v>135136001</v>
       </c>
       <c r="B21" t="n">
         <v>99112</v>
@@ -2941,7 +2922,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2960,10 +2941,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499899</v>
+        <v>499871</v>
       </c>
       <c r="R21" t="n">
-        <v>6621248</v>
+        <v>6621255</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2995,7 +2976,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +2986,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,7 +3013,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135136115</v>
+        <v>135136063</v>
       </c>
       <c r="B22" t="n">
         <v>99112</v>
@@ -3062,7 +3043,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3081,10 +3062,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499917</v>
+        <v>499899</v>
       </c>
       <c r="R22" t="n">
-        <v>6621282</v>
+        <v>6621248</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3116,7 +3097,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3126,7 +3107,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,7 +3134,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135136391</v>
+        <v>135136115</v>
       </c>
       <c r="B23" t="n">
         <v>99112</v>
@@ -3183,7 +3164,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3202,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499940</v>
+        <v>499917</v>
       </c>
       <c r="R23" t="n">
-        <v>6621317</v>
+        <v>6621282</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3237,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3247,7 +3228,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,7 +3255,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135136466</v>
+        <v>135136391</v>
       </c>
       <c r="B24" t="n">
         <v>99112</v>
@@ -3304,7 +3285,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3323,10 +3304,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499950</v>
+        <v>499940</v>
       </c>
       <c r="R24" t="n">
-        <v>6621333</v>
+        <v>6621317</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3358,7 +3339,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3368,7 +3349,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,7 +3376,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135136984</v>
+        <v>135136466</v>
       </c>
       <c r="B25" t="n">
         <v>99112</v>
@@ -3425,7 +3406,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3444,10 +3425,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499932</v>
+        <v>499950</v>
       </c>
       <c r="R25" t="n">
-        <v>6621423</v>
+        <v>6621333</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3479,7 +3460,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3489,7 +3470,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,7 +3497,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135137057</v>
+        <v>135136984</v>
       </c>
       <c r="B26" t="n">
         <v>99112</v>
@@ -3546,7 +3527,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3565,10 +3546,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499912</v>
+        <v>499932</v>
       </c>
       <c r="R26" t="n">
-        <v>6621430</v>
+        <v>6621423</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3600,7 +3581,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3610,7 +3591,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3637,7 +3618,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135137666</v>
+        <v>135137057</v>
       </c>
       <c r="B27" t="n">
         <v>99112</v>
@@ -3667,7 +3648,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3686,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499790</v>
+        <v>499912</v>
       </c>
       <c r="R27" t="n">
-        <v>6621466</v>
+        <v>6621430</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3721,7 +3702,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3731,7 +3712,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3758,10 +3739,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134232855</v>
+        <v>135137666</v>
       </c>
       <c r="B28" t="n">
-        <v>98060</v>
+        <v>99112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3769,41 +3750,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499858</v>
+        <v>499790</v>
       </c>
       <c r="R28" t="n">
-        <v>6621241</v>
+        <v>6621466</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3827,27 +3818,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3862,19 +3848,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134232856</v>
+        <v>134232855</v>
       </c>
       <c r="B29" t="n">
         <v>98060</v>
@@ -3913,10 +3899,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499825</v>
+        <v>499858</v>
       </c>
       <c r="R29" t="n">
-        <v>6621232</v>
+        <v>6621241</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3934,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,7 +3944,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3987,6 +3973,122 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134232856</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>499825</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6621232</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135137492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135135968</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135191221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135137648</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1819,6 +1869,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232906</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1935,6 +1990,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232907</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232908</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232909</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2288,6 +2358,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134139</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134238</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2530,6 +2610,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134506</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2651,6 +2736,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134677</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135134706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2889,6 +2984,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135135788</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3010,6 +3110,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136001</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3131,6 +3236,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136063</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3252,6 +3362,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136115</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3373,6 +3488,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136391</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3494,6 +3614,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136466</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3615,6 +3740,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135136984</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3736,6 +3866,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135137057</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3857,6 +3992,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135137666</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3973,6 +4113,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232855</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4089,8 +4234,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135136407</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135134046</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135136673</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>135137492</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>135135968</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>135136960</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>135152620</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>135191221</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>135137648</v>
       </c>
       <c r="B10" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>135134139</v>
       </c>
       <c r="B15" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>135134238</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135134506</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135134677</v>
       </c>
       <c r="B18" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135134706</v>
       </c>
       <c r="B19" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>135135788</v>
       </c>
       <c r="B20" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>135136001</v>
       </c>
       <c r="B21" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135136063</v>
       </c>
       <c r="B22" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135136115</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135136391</v>
       </c>
       <c r="B24" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>135136466</v>
       </c>
       <c r="B25" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135136984</v>
       </c>
       <c r="B26" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135137057</v>
       </c>
       <c r="B27" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>135137666</v>
       </c>
       <c r="B28" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -2243,7 +2243,7 @@
         <v>135134139</v>
       </c>
       <c r="B15" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>135134238</v>
       </c>
       <c r="B16" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135134506</v>
       </c>
       <c r="B17" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135134677</v>
       </c>
       <c r="B18" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135134706</v>
       </c>
       <c r="B19" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>135135788</v>
       </c>
       <c r="B20" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>135136001</v>
       </c>
       <c r="B21" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135136063</v>
       </c>
       <c r="B22" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135136115</v>
       </c>
       <c r="B23" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135136391</v>
       </c>
       <c r="B24" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>135136466</v>
       </c>
       <c r="B25" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135136984</v>
       </c>
       <c r="B26" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135137057</v>
       </c>
       <c r="B27" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>135137666</v>
       </c>
       <c r="B28" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27732-2026 artfynd.xlsx
+++ b/artfynd/A 27732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135137648</v>
+        <v>135191221</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,39 +1538,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Kviddtjärnen, Gränsjön, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499790</v>
+        <v>499962</v>
       </c>
       <c r="R9" t="n">
-        <v>6621466</v>
+        <v>6621359</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1597,27 +1597,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Och kläckhål.</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,16 +1628,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135137648</t>
+          <t>https://artportalen.se/Sighting/135191221</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134232906</v>
+        <v>135137648</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,41 +1645,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499887</v>
+        <v>499790</v>
       </c>
       <c r="R10" t="n">
-        <v>6621451</v>
+        <v>6621466</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,27 +1704,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Och kläckhål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,24 +1739,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232906</t>
+          <t>https://artportalen.se/Sighting/135137648</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134232907</v>
+        <v>134232906</v>
       </c>
       <c r="B11" t="n">
         <v>99112</v>
@@ -1809,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499863</v>
+        <v>499887</v>
       </c>
       <c r="R11" t="n">
-        <v>6621478</v>
+        <v>6621451</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1844,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1885,13 +1871,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232907</t>
+          <t>https://artportalen.se/Sighting/134232906</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134232908</v>
+        <v>134232907</v>
       </c>
       <c r="B12" t="n">
         <v>99112</v>
@@ -1930,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499922</v>
+        <v>499863</v>
       </c>
       <c r="R12" t="n">
-        <v>6621337</v>
+        <v>6621478</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1965,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2006,13 +1992,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232908</t>
+          <t>https://artportalen.se/Sighting/134232907</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134232909</v>
+        <v>134232908</v>
       </c>
       <c r="B13" t="n">
         <v>99112</v>
@@ -2051,13 +2037,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499860</v>
+        <v>499922</v>
       </c>
       <c r="R13" t="n">
-        <v>6621240</v>
+        <v>6621337</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2086,7 +2072,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2082,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2127,16 +2113,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232909</t>
+          <t>https://artportalen.se/Sighting/134232908</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135134139</v>
+        <v>134232909</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,29 +2152,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499712</v>
+        <v>499860</v>
       </c>
       <c r="R14" t="n">
-        <v>6621314</v>
+        <v>6621240</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2212,22 +2188,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,24 +2223,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135134139</t>
+          <t>https://artportalen.se/Sighting/134232909</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135134238</v>
+        <v>135134139</v>
       </c>
       <c r="B15" t="n">
         <v>99186</v>
@@ -2289,7 +2270,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2308,7 +2289,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499725</v>
+        <v>499712</v>
       </c>
       <c r="R15" t="n">
         <v>6621314</v>
@@ -2343,7 +2324,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2353,7 +2334,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,13 +2360,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135134238</t>
+          <t>https://artportalen.se/Sighting/135134139</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135134506</v>
+        <v>135134238</v>
       </c>
       <c r="B16" t="n">
         <v>99186</v>
@@ -2415,7 +2396,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2434,10 +2415,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499755</v>
+        <v>499725</v>
       </c>
       <c r="R16" t="n">
-        <v>6621280</v>
+        <v>6621314</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2469,7 +2450,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2479,7 +2460,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,13 +2486,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135134506</t>
+          <t>https://artportalen.se/Sighting/135134238</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135134677</v>
+        <v>135134506</v>
       </c>
       <c r="B17" t="n">
         <v>99186</v>
@@ -2541,7 +2522,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2560,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499824</v>
+        <v>499755</v>
       </c>
       <c r="R17" t="n">
-        <v>6621297</v>
+        <v>6621280</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2595,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2605,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,13 +2612,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135134677</t>
+          <t>https://artportalen.se/Sighting/135134506</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135134706</v>
+        <v>135134677</v>
       </c>
       <c r="B18" t="n">
         <v>99186</v>
@@ -2665,7 +2646,11 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2682,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499838</v>
+        <v>499824</v>
       </c>
       <c r="R18" t="n">
-        <v>6621289</v>
+        <v>6621297</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2717,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2727,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,13 +2738,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135134706</t>
+          <t>https://artportalen.se/Sighting/135134677</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135135788</v>
+        <v>135134706</v>
       </c>
       <c r="B19" t="n">
         <v>99186</v>
@@ -2787,11 +2772,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2808,10 +2789,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499855</v>
+        <v>499838</v>
       </c>
       <c r="R19" t="n">
-        <v>6621252</v>
+        <v>6621289</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2843,7 +2824,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2853,7 +2834,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2879,13 +2860,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135135788</t>
+          <t>https://artportalen.se/Sighting/135134706</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135136001</v>
+        <v>135135788</v>
       </c>
       <c r="B20" t="n">
         <v>99186</v>
@@ -2915,7 +2896,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2934,10 +2915,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499871</v>
+        <v>499855</v>
       </c>
       <c r="R20" t="n">
-        <v>6621255</v>
+        <v>6621252</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2969,7 +2950,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2979,7 +2960,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3005,13 +2986,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136001</t>
+          <t>https://artportalen.se/Sighting/135135788</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135136063</v>
+        <v>135136001</v>
       </c>
       <c r="B21" t="n">
         <v>99186</v>
@@ -3041,7 +3022,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3060,10 +3041,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499899</v>
+        <v>499871</v>
       </c>
       <c r="R21" t="n">
-        <v>6621248</v>
+        <v>6621255</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3095,7 +3076,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3105,7 +3086,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3131,13 +3112,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136063</t>
+          <t>https://artportalen.se/Sighting/135136001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135136115</v>
+        <v>135136063</v>
       </c>
       <c r="B22" t="n">
         <v>99186</v>
@@ -3167,7 +3148,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3186,10 +3167,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499917</v>
+        <v>499899</v>
       </c>
       <c r="R22" t="n">
-        <v>6621282</v>
+        <v>6621248</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3221,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3231,7 +3212,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3257,13 +3238,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136115</t>
+          <t>https://artportalen.se/Sighting/135136063</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135136391</v>
+        <v>135136115</v>
       </c>
       <c r="B23" t="n">
         <v>99186</v>
@@ -3293,7 +3274,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3312,10 +3293,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499940</v>
+        <v>499917</v>
       </c>
       <c r="R23" t="n">
-        <v>6621317</v>
+        <v>6621282</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3347,7 +3328,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3357,7 +3338,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3383,13 +3364,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136391</t>
+          <t>https://artportalen.se/Sighting/135136115</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135136466</v>
+        <v>135136391</v>
       </c>
       <c r="B24" t="n">
         <v>99186</v>
@@ -3419,7 +3400,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3438,10 +3419,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499950</v>
+        <v>499940</v>
       </c>
       <c r="R24" t="n">
-        <v>6621333</v>
+        <v>6621317</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3473,7 +3454,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3483,7 +3464,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3509,13 +3490,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136466</t>
+          <t>https://artportalen.se/Sighting/135136391</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135136984</v>
+        <v>135136466</v>
       </c>
       <c r="B25" t="n">
         <v>99186</v>
@@ -3545,7 +3526,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3564,10 +3545,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499932</v>
+        <v>499950</v>
       </c>
       <c r="R25" t="n">
-        <v>6621423</v>
+        <v>6621333</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3599,7 +3580,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3609,7 +3590,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3635,13 +3616,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135136984</t>
+          <t>https://artportalen.se/Sighting/135136466</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135137057</v>
+        <v>135136984</v>
       </c>
       <c r="B26" t="n">
         <v>99186</v>
@@ -3671,7 +3652,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3690,10 +3671,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499912</v>
+        <v>499932</v>
       </c>
       <c r="R26" t="n">
-        <v>6621430</v>
+        <v>6621423</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3725,7 +3706,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3716,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3761,13 +3742,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135137057</t>
+          <t>https://artportalen.se/Sighting/135136984</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135137666</v>
+        <v>135137057</v>
       </c>
       <c r="B27" t="n">
         <v>99186</v>
@@ -3797,7 +3778,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3816,10 +3797,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499790</v>
+        <v>499912</v>
       </c>
       <c r="R27" t="n">
-        <v>6621466</v>
+        <v>6621430</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3851,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3861,7 +3842,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3887,16 +3868,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135137666</t>
+          <t>https://artportalen.se/Sighting/135137057</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134232855</v>
+        <v>135137666</v>
       </c>
       <c r="B28" t="n">
-        <v>98060</v>
+        <v>99186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,41 +3885,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499858</v>
+        <v>499790</v>
       </c>
       <c r="R28" t="n">
-        <v>6621241</v>
+        <v>6621466</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3962,27 +3953,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3997,24 +3983,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232855</t>
+          <t>https://artportalen.se/Sighting/135137666</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134232856</v>
+        <v>134232855</v>
       </c>
       <c r="B29" t="n">
         <v>98060</v>
@@ -4053,10 +4039,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499825</v>
+        <v>499858</v>
       </c>
       <c r="R29" t="n">
-        <v>6621232</v>
+        <v>6621241</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4088,7 +4074,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4098,7 +4084,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4128,6 +4114,127 @@
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232855</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134232856</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>499825</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6621232</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134232856</t>
         </is>
@@ -4163,6 +4270,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
